--- a/research/traditional_assets/database/data/qatar/qatar_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0673</v>
+        <v>0.282</v>
       </c>
       <c r="E2">
-        <v>0.0462</v>
+        <v>0.0883</v>
       </c>
       <c r="G2">
-        <v>0.448742746615087</v>
+        <v>0.2674943566591422</v>
       </c>
       <c r="H2">
-        <v>0.448742746615087</v>
+        <v>0.2674943566591422</v>
       </c>
       <c r="I2">
-        <v>0.4738878143133462</v>
+        <v>0.2708803611738149</v>
       </c>
       <c r="J2">
-        <v>0.4738878143133462</v>
+        <v>0.2708803611738149</v>
       </c>
       <c r="K2">
-        <v>21</v>
+        <v>26.6</v>
       </c>
       <c r="L2">
-        <v>0.4061895551257253</v>
+        <v>0.3002257336343115</v>
       </c>
       <c r="M2">
-        <v>13.8</v>
+        <v>15.8</v>
       </c>
       <c r="N2">
-        <v>0.04186893203883495</v>
+        <v>0.04407252440725244</v>
       </c>
       <c r="O2">
-        <v>0.6571428571428571</v>
+        <v>0.5939849624060151</v>
       </c>
       <c r="P2">
-        <v>13.8</v>
+        <v>15.8</v>
       </c>
       <c r="Q2">
-        <v>0.04186893203883495</v>
+        <v>0.04407252440725244</v>
       </c>
       <c r="R2">
-        <v>0.6571428571428571</v>
+        <v>0.5939849624060151</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>94.40000000000001</v>
+        <v>50.7</v>
       </c>
       <c r="V2">
-        <v>0.2864077669902912</v>
+        <v>0.1414225941422594</v>
       </c>
       <c r="W2">
-        <v>0.2009569377990431</v>
+        <v>0.2383512544802868</v>
       </c>
       <c r="X2">
-        <v>0.04818892356739694</v>
+        <v>0.0813679571463031</v>
       </c>
       <c r="Y2">
-        <v>0.1527680142316461</v>
+        <v>0.1569832973339837</v>
       </c>
       <c r="Z2">
-        <v>2.118852459016393</v>
+        <v>4.898004312012829</v>
       </c>
       <c r="AA2">
-        <v>1.004098360655737</v>
+        <v>1.326773177068938</v>
       </c>
       <c r="AB2">
-        <v>0.04812826858301168</v>
+        <v>0.08133207283282796</v>
       </c>
       <c r="AC2">
-        <v>0.9559700920727258</v>
+        <v>1.24544110423611</v>
       </c>
       <c r="AD2">
-        <v>0.889</v>
+        <v>0.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.889</v>
+        <v>0.4</v>
       </c>
       <c r="AG2">
-        <v>-93.51100000000001</v>
+        <v>-50.3</v>
       </c>
       <c r="AH2">
-        <v>0.002689953372124337</v>
+        <v>0.001114516578434104</v>
       </c>
       <c r="AI2">
-        <v>0.007902994959507153</v>
+        <v>0.003294892915980231</v>
       </c>
       <c r="AJ2">
-        <v>-0.3960836803070029</v>
+        <v>-0.1632057105775471</v>
       </c>
       <c r="AK2">
-        <v>-5.169495273370561</v>
+        <v>-0.7114568599717116</v>
       </c>
       <c r="AL2">
-        <v>0.013</v>
+        <v>0.03</v>
       </c>
       <c r="AM2">
-        <v>0.013</v>
+        <v>0.03</v>
       </c>
       <c r="AN2">
-        <v>0.03393129770992367</v>
+        <v>0.01550387596899225</v>
       </c>
       <c r="AO2">
-        <v>1884.615384615385</v>
+        <v>800</v>
       </c>
       <c r="AP2">
-        <v>-3.569122137404581</v>
+        <v>-1.949612403100775</v>
       </c>
       <c r="AQ2">
-        <v>1884.615384615385</v>
+        <v>800</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Qatar Islamic Insurance Group  Q.P.S.C. (DSM:QISI)</t>
+          <t>Qatar Islamic Insurance Group Q.P.S.C. (DSM:QISI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0673</v>
+        <v>0.282</v>
       </c>
       <c r="E3">
-        <v>0.0462</v>
+        <v>0.0883</v>
       </c>
       <c r="G3">
-        <v>0.448742746615087</v>
+        <v>0.2674943566591422</v>
       </c>
       <c r="H3">
-        <v>0.448742746615087</v>
+        <v>0.2674943566591422</v>
       </c>
       <c r="I3">
-        <v>0.4738878143133462</v>
+        <v>0.2708803611738149</v>
       </c>
       <c r="J3">
-        <v>0.4738878143133462</v>
+        <v>0.2708803611738149</v>
       </c>
       <c r="K3">
-        <v>21</v>
+        <v>26.6</v>
       </c>
       <c r="L3">
-        <v>0.4061895551257253</v>
+        <v>0.3002257336343115</v>
       </c>
       <c r="M3">
-        <v>13.8</v>
+        <v>15.8</v>
       </c>
       <c r="N3">
-        <v>0.04186893203883495</v>
+        <v>0.04407252440725244</v>
       </c>
       <c r="O3">
-        <v>0.6571428571428571</v>
+        <v>0.5939849624060151</v>
       </c>
       <c r="P3">
-        <v>13.8</v>
+        <v>15.8</v>
       </c>
       <c r="Q3">
-        <v>0.04186893203883495</v>
+        <v>0.04407252440725244</v>
       </c>
       <c r="R3">
-        <v>0.6571428571428571</v>
+        <v>0.5939849624060151</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>94.40000000000001</v>
+        <v>50.7</v>
       </c>
       <c r="V3">
-        <v>0.2864077669902912</v>
+        <v>0.1414225941422594</v>
       </c>
       <c r="W3">
-        <v>0.2009569377990431</v>
+        <v>0.2383512544802868</v>
       </c>
       <c r="X3">
-        <v>0.04818892356739694</v>
+        <v>0.0813679571463031</v>
       </c>
       <c r="Y3">
-        <v>0.1527680142316461</v>
+        <v>0.1569832973339837</v>
       </c>
       <c r="Z3">
-        <v>2.118852459016393</v>
+        <v>4.898004312012829</v>
       </c>
       <c r="AA3">
-        <v>1.004098360655737</v>
+        <v>1.326773177068938</v>
       </c>
       <c r="AB3">
-        <v>0.04812826858301168</v>
+        <v>0.08133207283282796</v>
       </c>
       <c r="AC3">
-        <v>0.9559700920727258</v>
+        <v>1.24544110423611</v>
       </c>
       <c r="AD3">
-        <v>0.889</v>
+        <v>0.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.889</v>
+        <v>0.4</v>
       </c>
       <c r="AG3">
-        <v>-93.51100000000001</v>
+        <v>-50.3</v>
       </c>
       <c r="AH3">
-        <v>0.002689953372124337</v>
+        <v>0.001114516578434104</v>
       </c>
       <c r="AI3">
-        <v>0.007902994959507153</v>
+        <v>0.003294892915980231</v>
       </c>
       <c r="AJ3">
-        <v>-0.3960836803070029</v>
+        <v>-0.1632057105775471</v>
       </c>
       <c r="AK3">
-        <v>-5.169495273370561</v>
+        <v>-0.7114568599717116</v>
       </c>
       <c r="AL3">
-        <v>0.013</v>
+        <v>0.03</v>
       </c>
       <c r="AM3">
-        <v>0.013</v>
+        <v>0.03</v>
       </c>
       <c r="AN3">
-        <v>0.03393129770992367</v>
+        <v>0.01550387596899225</v>
       </c>
       <c r="AO3">
-        <v>1884.615384615385</v>
+        <v>800</v>
       </c>
       <c r="AP3">
-        <v>-3.569122137404581</v>
+        <v>-1.949612403100775</v>
       </c>
       <c r="AQ3">
-        <v>1884.615384615385</v>
+        <v>800</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/qatar/qatar_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,47 +587,44 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D2">
-        <v>0.282</v>
-      </c>
       <c r="E2">
-        <v>0.0883</v>
+        <v>0.125</v>
       </c>
       <c r="G2">
-        <v>0.2674943566591422</v>
+        <v>0.3196251952108277</v>
       </c>
       <c r="H2">
-        <v>0.2674943566591422</v>
+        <v>0.3196251952108277</v>
       </c>
       <c r="I2">
-        <v>0.2708803611738149</v>
+        <v>0.3425299323269131</v>
       </c>
       <c r="J2">
-        <v>0.2708803611738149</v>
+        <v>0.3417086244966125</v>
       </c>
       <c r="K2">
-        <v>26.6</v>
+        <v>61.09999999999999</v>
       </c>
       <c r="L2">
-        <v>0.3002257336343115</v>
+        <v>0.3180635085892763</v>
       </c>
       <c r="M2">
-        <v>15.8</v>
+        <v>29.2</v>
       </c>
       <c r="N2">
-        <v>0.04407252440725244</v>
+        <v>0.04984636394673951</v>
       </c>
       <c r="O2">
-        <v>0.5939849624060151</v>
+        <v>0.4779050736497546</v>
       </c>
       <c r="P2">
-        <v>15.8</v>
+        <v>29.2</v>
       </c>
       <c r="Q2">
-        <v>0.04407252440725244</v>
+        <v>0.04984636394673951</v>
       </c>
       <c r="R2">
-        <v>0.5939849624060151</v>
+        <v>0.4779050736497546</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +633,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>50.7</v>
+        <v>157.7</v>
       </c>
       <c r="V2">
-        <v>0.1414225941422594</v>
+        <v>0.2692045066575623</v>
       </c>
       <c r="W2">
-        <v>0.2383512544802868</v>
+        <v>0.2513021766013664</v>
       </c>
       <c r="X2">
-        <v>0.0813679571463031</v>
+        <v>0.07342421405564793</v>
       </c>
       <c r="Y2">
-        <v>0.1569832973339837</v>
+        <v>0.1778779625457185</v>
       </c>
       <c r="Z2">
-        <v>4.898004312012829</v>
+        <v>0.8980832164562882</v>
       </c>
       <c r="AA2">
-        <v>1.326773177068938</v>
+        <v>0.3678607920731861</v>
       </c>
       <c r="AB2">
-        <v>0.08133207283282796</v>
+        <v>0.07308703945878742</v>
       </c>
       <c r="AC2">
-        <v>1.24544110423611</v>
+        <v>0.2947737526143987</v>
       </c>
       <c r="AD2">
-        <v>0.4</v>
+        <v>7.733000000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.4</v>
+        <v>7.733000000000001</v>
       </c>
       <c r="AG2">
-        <v>-50.3</v>
+        <v>-149.967</v>
       </c>
       <c r="AH2">
-        <v>0.001114516578434104</v>
+        <v>0.01302876166952807</v>
       </c>
       <c r="AI2">
-        <v>0.003294892915980231</v>
+        <v>0.02809619486035468</v>
       </c>
       <c r="AJ2">
-        <v>-0.1632057105775471</v>
+        <v>-0.3440928061895267</v>
       </c>
       <c r="AK2">
-        <v>-0.7114568599717116</v>
+        <v>-1.275956539865399</v>
       </c>
       <c r="AL2">
-        <v>0.03</v>
+        <v>0.163</v>
       </c>
       <c r="AM2">
-        <v>0.03</v>
+        <v>0.163</v>
       </c>
       <c r="AN2">
-        <v>0.01550387596899225</v>
+        <v>0.1137205882352941</v>
       </c>
       <c r="AO2">
-        <v>800</v>
+        <v>403.6809815950921</v>
       </c>
       <c r="AP2">
-        <v>-1.949612403100775</v>
+        <v>-2.205397058823529</v>
       </c>
       <c r="AQ2">
-        <v>800</v>
+        <v>403.6809815950921</v>
       </c>
     </row>
     <row r="3">
@@ -721,47 +718,44 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.282</v>
-      </c>
       <c r="E3">
-        <v>0.0883</v>
+        <v>0.125</v>
       </c>
       <c r="G3">
-        <v>0.2674943566591422</v>
+        <v>0.2947269303201507</v>
       </c>
       <c r="H3">
-        <v>0.2674943566591422</v>
+        <v>0.2947269303201507</v>
       </c>
       <c r="I3">
-        <v>0.2708803611738149</v>
+        <v>0.364406779661017</v>
       </c>
       <c r="J3">
-        <v>0.2708803611738149</v>
+        <v>0.364406779661017</v>
       </c>
       <c r="K3">
-        <v>26.6</v>
+        <v>34.3</v>
       </c>
       <c r="L3">
-        <v>0.3002257336343115</v>
+        <v>0.3229755178907721</v>
       </c>
       <c r="M3">
-        <v>15.8</v>
+        <v>18.6</v>
       </c>
       <c r="N3">
-        <v>0.04407252440725244</v>
+        <v>0.05072266157622035</v>
       </c>
       <c r="O3">
-        <v>0.5939849624060151</v>
+        <v>0.5422740524781342</v>
       </c>
       <c r="P3">
-        <v>15.8</v>
+        <v>18.6</v>
       </c>
       <c r="Q3">
-        <v>0.04407252440725244</v>
+        <v>0.05072266157622035</v>
       </c>
       <c r="R3">
-        <v>0.5939849624060151</v>
+        <v>0.5422740524781342</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +764,201 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>50.7</v>
+        <v>123.3</v>
       </c>
       <c r="V3">
-        <v>0.1414225941422594</v>
+        <v>0.3362421598036542</v>
       </c>
       <c r="W3">
-        <v>0.2383512544802868</v>
+        <v>0.2834710743801653</v>
       </c>
       <c r="X3">
-        <v>0.0813679571463031</v>
+        <v>0.07291442291493919</v>
       </c>
       <c r="Y3">
-        <v>0.1569832973339837</v>
+        <v>0.2105566514652261</v>
       </c>
       <c r="Z3">
-        <v>4.898004312012829</v>
+        <v>1.502121640735502</v>
       </c>
       <c r="AA3">
-        <v>1.326773177068938</v>
+        <v>0.5473833097595474</v>
       </c>
       <c r="AB3">
-        <v>0.08133207283282796</v>
+        <v>0.07289398854142709</v>
       </c>
       <c r="AC3">
-        <v>1.24544110423611</v>
+        <v>0.4744893212181203</v>
       </c>
       <c r="AD3">
-        <v>0.4</v>
+        <v>0.283</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.4</v>
+        <v>0.283</v>
       </c>
       <c r="AG3">
-        <v>-50.3</v>
+        <v>-123.017</v>
       </c>
       <c r="AH3">
-        <v>0.001114516578434104</v>
+        <v>0.0007711528871909597</v>
       </c>
       <c r="AI3">
-        <v>0.003294892915980231</v>
+        <v>0.002099671323534867</v>
       </c>
       <c r="AJ3">
-        <v>-0.1632057105775471</v>
+        <v>-0.5048238900538815</v>
       </c>
       <c r="AK3">
-        <v>-0.7114568599717116</v>
+        <v>-10.7129669946878</v>
       </c>
       <c r="AL3">
-        <v>0.03</v>
+        <v>0.014</v>
       </c>
       <c r="AM3">
-        <v>0.03</v>
+        <v>0.014</v>
       </c>
       <c r="AN3">
-        <v>0.01550387596899225</v>
+        <v>0.007237851662404091</v>
       </c>
       <c r="AO3">
-        <v>800</v>
+        <v>2764.285714285714</v>
       </c>
       <c r="AP3">
-        <v>-1.949612403100775</v>
+        <v>-3.146214833759591</v>
       </c>
       <c r="AQ3">
-        <v>800</v>
+        <v>2764.285714285714</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Damaan Islamic Insurance Company "Beema" (Q.P.S.C.) (DSM:BEMA)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>0.350407450523865</v>
+      </c>
+      <c r="H4">
+        <v>0.350407450523865</v>
+      </c>
+      <c r="I4">
+        <v>0.3154831199068684</v>
+      </c>
+      <c r="J4">
+        <v>0.3139702082909582</v>
+      </c>
+      <c r="K4">
+        <v>26.8</v>
+      </c>
+      <c r="L4">
+        <v>0.3119906868451688</v>
+      </c>
+      <c r="M4">
+        <v>10.6</v>
+      </c>
+      <c r="N4">
+        <v>0.04837973528069375</v>
+      </c>
+      <c r="O4">
+        <v>0.3955223880597015</v>
+      </c>
+      <c r="P4">
+        <v>10.6</v>
+      </c>
+      <c r="Q4">
+        <v>0.04837973528069375</v>
+      </c>
+      <c r="R4">
+        <v>0.3955223880597015</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>34.4</v>
+      </c>
+      <c r="V4">
+        <v>0.1570059333637608</v>
+      </c>
+      <c r="W4">
+        <v>0.2191332788225675</v>
+      </c>
+      <c r="X4">
+        <v>0.07393400519635668</v>
+      </c>
+      <c r="Y4">
+        <v>0.1451992736262108</v>
+      </c>
+      <c r="Z4">
+        <v>0.5998603351955308</v>
+      </c>
+      <c r="AA4">
+        <v>0.1883382743868248</v>
+      </c>
+      <c r="AB4">
+        <v>0.07328009037614773</v>
+      </c>
+      <c r="AC4">
+        <v>0.1150581840106771</v>
+      </c>
+      <c r="AD4">
+        <v>7.45</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>7.45</v>
+      </c>
+      <c r="AG4">
+        <v>-26.95</v>
+      </c>
+      <c r="AH4">
+        <v>0.03288457294195542</v>
+      </c>
+      <c r="AI4">
+        <v>0.05304378782484871</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.1402550091074681</v>
+      </c>
+      <c r="AK4">
+        <v>-0.2541254125412541</v>
+      </c>
+      <c r="AL4">
+        <v>0.149</v>
+      </c>
+      <c r="AM4">
+        <v>0.149</v>
+      </c>
+      <c r="AN4">
+        <v>0.2577854671280277</v>
+      </c>
+      <c r="AO4">
+        <v>181.8791946308725</v>
+      </c>
+      <c r="AP4">
+        <v>-0.9325259515570935</v>
+      </c>
+      <c r="AQ4">
+        <v>181.8791946308725</v>
       </c>
     </row>
   </sheetData>
